--- a/data/events/data.xlsx
+++ b/data/events/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\n11601\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D795ED-E7ED-4946-B75D-0E3DF9A2885A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5E7450F-8270-4FF5-B7C4-CAA6BFDA02F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{906532D7-D4E8-4E75-B1C3-50E8851F01AD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{246595B6-AE50-4B12-A34C-D2F56FA0F0A4}"/>
   </bookViews>
   <sheets>
     <sheet name="オープンデータ" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="302">
   <si>
     <t>№</t>
     <phoneticPr fontId="4"/>
@@ -1419,7 +1419,7 @@
     <t>087-812-7534</t>
   </si>
   <si>
-    <t>5月18日(月)～20日(水)予定</t>
+    <t>5月18日(月)～20日(水)</t>
     <rPh sb="5" eb="6">
       <t>ド</t>
     </rPh>
@@ -1450,26 +1450,44 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>B3 PLAYOFFS FINALS 2025-26
 （香川ファイブアローズ）
-対戦相手：未定</t>
+対戦相手：立川ダイス</t>
+    <rPh sb="45" eb="47">
+      <t>タチカワ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>あなぶきアリーナ香川
 （香川県立アリーナ）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>地域密着型トップスポーツチームの公式戦ホームゲームです。
-※５月９日（土）～５月１１日（月）の準決勝で敗退した場合は、試合はありません。</t>
-    <rPh sb="35" eb="36">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ゲツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>34.353409024567874</t>
+  </si>
+  <si>
+    <t>134.04493644831683</t>
+  </si>
+  <si>
+    <t>地域密着型トップスポーツチームの公式戦ホームゲームです。</t>
+  </si>
+  <si>
+    <t>席種により異なります</t>
+  </si>
+  <si>
+    <t>香川ファイブアローズオフィシャルサイト
+https://www.fivearrows.jp/</t>
+  </si>
+  <si>
+    <t>香川ファイブアローズ
+(高松市スポーツ振興課)</t>
+  </si>
+  <si>
+    <t>087-813-7120
+(087-839-2626)</t>
   </si>
   <si>
     <t>5月19日（火）</t>
@@ -2488,9 +2506,6 @@
       <t>チイキミッチャクガタ</t>
     </rPh>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>席種により異なります</t>
   </si>
   <si>
     <t>カマタマーレ讃岐オフィシャルサイト
@@ -3458,13 +3473,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3501,6 +3516,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3588,18 +3615,6 @@
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3935,25 +3950,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5843E2B4-0B43-43E3-B6C5-5BBA7D9622CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B80B22-D63A-4DF6-AEBA-F68E2780A3D2}">
   <sheetPr>
+    <tabColor rgb="FFFF99FF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W34"/>
   <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="12.69921875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="20" style="28" customWidth="1"/>
-    <col min="4" max="5" width="12.69921875" style="29" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" style="27" customWidth="1"/>
-    <col min="7" max="7" width="24.8984375" style="27" customWidth="1"/>
-    <col min="8" max="9" width="20.69921875" style="28" customWidth="1"/>
-    <col min="10" max="10" width="35" style="27" customWidth="1"/>
-    <col min="11" max="12" width="11.69921875" style="27" customWidth="1"/>
-    <col min="13" max="13" width="18.09765625" style="30" customWidth="1"/>
-    <col min="14" max="14" width="24.69921875" style="27" customWidth="1"/>
-    <col min="15" max="16" width="20.69921875" style="27" customWidth="1"/>
+    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" style="31" customWidth="1"/>
+    <col min="3" max="3" width="20" style="32" customWidth="1"/>
+    <col min="4" max="5" width="12.69921875" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" style="31" customWidth="1"/>
+    <col min="7" max="7" width="24.8984375" style="31" customWidth="1"/>
+    <col min="8" max="9" width="20.69921875" style="32" customWidth="1"/>
+    <col min="10" max="10" width="35" style="31" customWidth="1"/>
+    <col min="11" max="12" width="11.69921875" style="31" customWidth="1"/>
+    <col min="13" max="13" width="18.09765625" style="34" customWidth="1"/>
+    <col min="14" max="14" width="24.69921875" style="31" customWidth="1"/>
+    <col min="15" max="16" width="20.69921875" style="31" customWidth="1"/>
     <col min="17" max="22" width="2.09765625" style="1" customWidth="1"/>
     <col min="23" max="26" width="15.59765625" style="1" customWidth="1"/>
     <col min="27" max="27" width="5.59765625" style="1" customWidth="1"/>
@@ -3962,1739 +3978,1739 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
+    <row r="2" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
+    <row r="3" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
+    <row r="4" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
+    <row r="5" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2">
+    <row r="6" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
+    <row r="7" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
+    <row r="8" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="2">
+    <row r="9" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="2">
+    <row r="10" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="O10" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="10" customFormat="1" ht="351.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="2">
+    <row r="11" spans="1:16" s="14" customFormat="1" ht="351.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="O11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="12" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="2">
+    <row r="12" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="O12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="P12" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="2">
+    <row r="13" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="O13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="10" customFormat="1" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="2">
+    <row r="14" spans="1:16" s="14" customFormat="1" ht="287.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="14" customFormat="1" ht="370.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="14" customFormat="1" ht="299.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="N16" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P22" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="14" customFormat="1" ht="409.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="14" customFormat="1" ht="279.60000000000002" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="14" customFormat="1" ht="384" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N27" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="14" customFormat="1" ht="348.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="K28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L28" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>87</v>
+      <c r="N28" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>228</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="10" customFormat="1" ht="370.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="29" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C29" s="16">
+        <v>46179</v>
+      </c>
+      <c r="D29" s="22">
+        <v>0.5625</v>
+      </c>
+      <c r="E29" s="22">
+        <v>0.625</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="M29" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="N29" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="14" customFormat="1" ht="278.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="21">
+        <v>46193</v>
+      </c>
+      <c r="D31" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="14" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>100</v>
+      <c r="E32" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="P32" s="12" t="s">
+        <v>265</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="10" customFormat="1" ht="299.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="K16" s="3" t="s">
+    <row r="33" spans="1:23" s="14" customFormat="1" ht="261.60000000000002" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="K33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>148</v>
-      </c>
+      <c r="L33" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="M33" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="W33" s="29"/>
     </row>
-    <row r="17" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K17" s="3" t="s">
+    <row r="34" spans="1:23" s="14" customFormat="1" ht="260.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="K34" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="N17" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="10" customFormat="1" ht="409.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="M24" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" s="10" customFormat="1" ht="279.60000000000002" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" s="10" customFormat="1" ht="384" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N27" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" s="10" customFormat="1" ht="348.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="12">
-        <v>46179</v>
-      </c>
-      <c r="D29" s="18">
-        <v>0.5625</v>
-      </c>
-      <c r="E29" s="18">
-        <v>0.625</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="N29" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="P29" s="8" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="10" customFormat="1" ht="278.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C31" s="17">
-        <v>46193</v>
-      </c>
-      <c r="D31" s="11">
-        <v>0.5625</v>
-      </c>
-      <c r="E31" s="11">
-        <v>0.625</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="N31" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" s="10" customFormat="1" ht="250.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="M32" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" s="10" customFormat="1" ht="261.60000000000002" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="M33" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="N33" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="W33" s="25"/>
-    </row>
-    <row r="34" spans="1:23" s="10" customFormat="1" ht="260.39999999999998" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="L34" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="M34" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L34" s="8" t="s">
+      <c r="N34" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="O34" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="M34" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="N34" s="13" t="s">
+      <c r="P34" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="O34" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="W34" s="25"/>
+      <c r="W34" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AO34" xr:uid="{56792E91-A9CD-40AE-AFB0-FDE1E8C8227D}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{3C7BAC6D-9EFB-4F8D-8E40-4D7E2D43F251}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B3" xr:uid="{D3F4BE4C-E866-4AD9-8DA8-21218E7747B9}">
       <formula1>$V$2:$V$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 B4:B1048576" xr:uid="{6FE7EAD0-23F4-4D99-B5A3-85B4494DC4FC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 B4:B1048576" xr:uid="{CE25C5D0-8CAB-4581-B5A2-29574F29116F}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N34" r:id="rId1" xr:uid="{22FDC965-6A36-469A-9574-0EE9FC83946B}"/>
-    <hyperlink ref="N29" r:id="rId2" xr:uid="{6159DBF2-F055-4A83-8B7E-8EBE78A57A35}"/>
-    <hyperlink ref="N6" r:id="rId3" xr:uid="{D12CAEC4-7ED3-4730-A479-175BC0097A89}"/>
-    <hyperlink ref="N4" r:id="rId4" xr:uid="{2D541F0C-2701-49F4-813D-D4BCCA9F9BD5}"/>
-    <hyperlink ref="N5" r:id="rId5" xr:uid="{AADB7E9B-DAD8-4CB1-9BD2-BDF0BF6045ED}"/>
-    <hyperlink ref="N8" r:id="rId6" xr:uid="{0FCEBFBE-1760-440F-AC54-23058E4656B5}"/>
-    <hyperlink ref="N12" r:id="rId7" xr:uid="{B561D479-E5A9-470E-9CD2-05058FD8D85C}"/>
-    <hyperlink ref="N19" r:id="rId8" xr:uid="{BDF8D73B-8CEB-4F61-A873-D9D465C0CFB4}"/>
-    <hyperlink ref="N2" r:id="rId9" xr:uid="{49430990-4DDD-4B9B-BB0E-8DA48B03D479}"/>
-    <hyperlink ref="N3" r:id="rId10" xr:uid="{A043AFF6-D7E4-402C-97B4-7BEDD441B5FD}"/>
-    <hyperlink ref="N7" r:id="rId11" xr:uid="{526480D1-700F-44F2-8C4B-A65F0649DC86}"/>
-    <hyperlink ref="N13" display="https://www.flat-takamatsu.net/bcs/info8306.html" xr:uid="{5B99BBFF-3BE3-4AB7-ADB2-09277C49B87D}"/>
-    <hyperlink ref="N20" display="https://www.flat-takamatsu.net/bcs/info8264.html" xr:uid="{4CCAD84C-D629-403B-A751-076070232074}"/>
-    <hyperlink ref="N22" display="https://www.flat-takamatsu.net/bcs/info8360.html" xr:uid="{D1716E3D-4FC7-4EB0-944F-248AA641232C}"/>
-    <hyperlink ref="N25" display="https://www.flat-takamatsu.net/bcs/info8310.html" xr:uid="{62B31B96-AC71-46F2-AB8D-12474EEFA636}"/>
-    <hyperlink ref="N30" r:id="rId12" xr:uid="{C2F0041F-0F7C-47FC-90AD-D7D7109DD559}"/>
-    <hyperlink ref="N32" r:id="rId13" xr:uid="{796C2D49-5CD5-47E0-BCD1-41B1CB8D78B0}"/>
-    <hyperlink ref="N23" r:id="rId14" xr:uid="{12161F74-B07A-4D50-BD3B-86335845BD12}"/>
-    <hyperlink ref="N9" r:id="rId15" xr:uid="{6A6A0095-5419-4C05-96FF-15478EAC4511}"/>
-    <hyperlink ref="N21" r:id="rId16" xr:uid="{E54E9B88-22E2-4083-A411-140627114C76}"/>
+    <hyperlink ref="N34" r:id="rId1" xr:uid="{4054A772-E7AB-429B-BDB5-92820C85A7A7}"/>
+    <hyperlink ref="N29" r:id="rId2" xr:uid="{A7D8FE8F-54D2-4397-A276-0E40F6ADD77A}"/>
+    <hyperlink ref="N6" r:id="rId3" xr:uid="{DDC6E180-E390-492F-AC5F-2D6E54428B16}"/>
+    <hyperlink ref="N4" r:id="rId4" xr:uid="{A454B32C-9335-47BA-B22A-5B5E755FF98B}"/>
+    <hyperlink ref="N5" r:id="rId5" xr:uid="{14CCD4F4-651D-45F5-A68B-2B77485DD8B9}"/>
+    <hyperlink ref="N8" r:id="rId6" xr:uid="{2BD35018-7A55-46E8-BD4D-AB1F2F7F5DFB}"/>
+    <hyperlink ref="N12" r:id="rId7" xr:uid="{316645CD-8B25-4F0C-87F8-285660F73AAE}"/>
+    <hyperlink ref="N19" r:id="rId8" xr:uid="{F0304EF6-748D-46B8-B074-930927E9DC1D}"/>
+    <hyperlink ref="N2" r:id="rId9" xr:uid="{9E2DF6DF-69F0-4233-B256-AF98E281B390}"/>
+    <hyperlink ref="N3" r:id="rId10" xr:uid="{3BDBFDA1-7E22-4099-97C6-46BEA9BDBBC4}"/>
+    <hyperlink ref="N7" r:id="rId11" xr:uid="{C3F1E7F0-8AC1-4F22-A8F6-8A64E0D60363}"/>
+    <hyperlink ref="N13" display="https://www.flat-takamatsu.net/bcs/info8306.html" xr:uid="{789E9A99-2B45-47F8-A821-1DAE6AD1E2F1}"/>
+    <hyperlink ref="N20" display="https://www.flat-takamatsu.net/bcs/info8264.html" xr:uid="{FE6EB91A-BEEB-4003-8DC1-C012B5A262AA}"/>
+    <hyperlink ref="N22" display="https://www.flat-takamatsu.net/bcs/info8360.html" xr:uid="{E6D6BB1D-52F6-4EAC-96F6-98B70E632525}"/>
+    <hyperlink ref="N25" display="https://www.flat-takamatsu.net/bcs/info8310.html" xr:uid="{47577FE6-A1AB-49B5-8B5E-8A02A4C93BD9}"/>
+    <hyperlink ref="N30" r:id="rId12" xr:uid="{09D06130-8D48-4E65-9320-675C56D831E6}"/>
+    <hyperlink ref="N32" r:id="rId13" xr:uid="{6B5A7739-F40E-4FAF-BE1C-9B00CBD5B918}"/>
+    <hyperlink ref="N23" r:id="rId14" xr:uid="{C5DE120A-E02B-4FA0-A442-843BB3AA5A07}"/>
+    <hyperlink ref="N9" r:id="rId15" xr:uid="{70FBD422-1658-44AF-BF0B-BC53033A2CEF}"/>
+    <hyperlink ref="N21" r:id="rId16" xr:uid="{B9CFC305-EC50-4B32-8095-253B21C926F6}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" cellComments="asDisplayed" r:id="rId17"/>
